--- a/docs/candidate_dataset_register.xlsx
+++ b/docs/candidate_dataset_register.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -700,6 +700,392 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>MAGIC Gamma Telescope</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>UCI, mirror: github.com/mikeizbicki/datasets/blob/master/csv/uci/magic04.data</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>19020</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Already binary. g means gamma ray, h means hadron.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>35.2% are hadron</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>no missing values</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Online Shoppers Purchasing Intention</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>UCI, mirror: github.com/sharmaroshan/Online-Shoppers-Purchasing-Intention</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>12330</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Already binary. Revenue is True if the visit ended in a purchase, False if not.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15.5% ended in a purchase</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>no missing values</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>EEG Eye State</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>UCI, mirror: github.com/Krishh-mishra98/eeg-eye-state-dataset</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>14980</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Already binary. 1 means eyes closed, 2 means eyes open (we treat this as 0/1).</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>44.9% eyes open</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>no missing values</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Rain in Australia (weatherAUS)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Kaggle: kaggle.com/datasets/jsphyg/weather-dataset-rattle-package, mirror: github.com/acakin/weatherAUS</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>142193 usable (145460 total, 3267 rows dropped for missing target)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16 (dropped Date, Location, and 4 columns over 30% missing: Sunshine, Evaporation, Cloud9am, Cloud3pm)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Already binary. RainTomorrow is Yes or No.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22.4% said Yes</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>worst kept column (Pressure9am) is 9.9% missing, after dropping the 4 columns above</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>From the Australian Bureau of Meteorology, shared on Kaggle. Check the Kaggle page for the exact reuse terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Diabetes 130-US Hospitals</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>UCI, mirror: github.com/swengzju/Predicting-Diabetes-Patient-Readmission</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>101766</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>42 (dropped 2 ID columns, and 5 columns over 30% missing: weight, max_glu_serum, A1Cresult, medical_specialty, payer_code)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Was 3 classes (NO, &lt;30, &gt;30 days). We made it binary: 1 = readmitted in under 30 days, 0 = not.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11.2% readmitted under 30 days</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>worst kept column (race) is 2.2% missing, after dropping the 5 columns above</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="55" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Letter Recognition</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>UCI, mirror: github.com/mikeizbicki/datasets/blob/master/csv/uci/letter-recognition.data</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Was 26 classes (one per letter). We made it binary: 1 = vowel (A, E, I, O, U), 0 = consonant.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19.4% vowels</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>no missing values</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="55" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Connect-4</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>UCI, mirror: github.com/ducanng/Decision-Tree-with-scikit-learn/blob/master/connect-4.data</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>67557</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Was 3 classes (win, loss, draw). We made it binary: 1 = win, 0 = not a win (loss or draw).</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>34.2% not a win</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>no missing values</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="55" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Statlog Shuttle (test split)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>UCI, mirror: github.com/mikeizbicki/datasets/blob/master/csv/uci/shuttle.tst</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>14500</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Was 7 classes. We made it binary: 1 = class 1 'Rad Flow', 0 = any other class.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>20.8% not class 1</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>no missing values</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>CC BY 4.0. Note: this is only the test portion of the full Statlog Shuttle dataset (the full set has about 58,000 rows). We could only get this file, so numbers here are for this 14,500-row file only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="55" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Nursery</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>UCI, mirror: github.com/mikeizbicki/datasets/blob/master/csv/uci/nursery.data</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>12960</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Was 5 classes. We made it binary: 1 = not_recom (application not recommended), 0 = any other outcome.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>33.3% not_recom</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>no missing values</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="55" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Chess (King-Rook vs King)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>UCI, mirror: github.com/mikeizbicki/datasets/blob/master/csv/uci/krkopt.data</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>28056</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Was 18 classes (draw, or number of moves to win). We made it binary: 1 = draw, 0 = White wins in some number of moves.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10.0% draw</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>no missing values</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -711,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -871,24 +1257,40 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>I looked at 13 datasets in total. 5 made it in, 8 did not.</t>
-        </is>
-      </c>
-    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>HTRU2 (Pulsar Detection)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>17898</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Row count looks fine (17,898) but we could not find a working raw file link to download and check it ourselves, so we left it out</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Main reason for rejecting: too few rows (6 out of 8).</t>
+          <t>I looked at 24 datasets in total across all rounds. 15 made it in, 9 did not.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Other reason: could not download the file myself to check the numbers (2 out of 8).</t>
+          <t>Main reason for rejecting: too few rows (6 out of 9).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Other reason: could not find a working download link to check the numbers ourselves (3 out of 9: Default of Credit Card Clients, Covertype, HTRU2).</t>
         </is>
       </c>
     </row>
@@ -908,7 +1310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -990,6 +1392,36 @@
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>I kept Give Me Some Credit in the list but flagged that competition rules are stricter and should be double checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="55" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>For datasets with more than 2 classes (Letter Recognition, Connect-4, Nursery, Chess, Shuttle), which class do we pick to turn it binary?</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>We picked the split that made the most real-world sense for each one (e.g. vowel vs consonant, win vs not-win, draw vs not-draw) rather than just picking the biggest class. A different choice would give a different minority percent, so this is a real decision, not just a formatting step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="55" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Is it OK to use just part of a dataset if that's the only file we could access?</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>For Statlog Shuttle, we could only get the 14,500-row test file, not the full ~58,000-row dataset. We used it anyway since it clears the 10,000-row minimum on its own, but we wrote clearly that it's only part of the full dataset so nobody assumes we checked the whole thing.</t>
         </is>
       </c>
     </row>

--- a/docs/candidate_dataset_register.xlsx
+++ b/docs/candidate_dataset_register.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,11 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="3">
@@ -77,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -85,8 +90,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -458,14 +462,14 @@
   <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -518,7 +522,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>UCI, mirror: github.com/jbrownlee/Datasets/blob/master/adult-all.csv</t>
+          <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/adult-all.csv</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -539,7 +543,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>workclass 5.7% missing, occupation 5.8% missing, native-country 1.8% missing</t>
+          <t>workclass 5.7% missing, occupation 5.8% missing, native_country 1.8% missing</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -556,7 +560,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>UCI/KEEL, mirror: github.com/jbrownlee/Datasets/blob/master/mammography.csv</t>
+          <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/mammography.csv</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -567,7 +571,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Already binary. 1 means calcification found, -1 means not found.</t>
+          <t>Already binary. class 1 means calcification found, -1 means not found.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -594,7 +598,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>kaggle.com/datasets/mlg-ulb/creditcardfraud</t>
+          <t>https://www.kaggle.com/datasets/mlg-ulb/creditcardfraud</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -632,7 +636,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>archive.ics.uci.edu/dataset/222/bank+marketing</t>
+          <t>https://raw.githubusercontent.com/khatrideepti/Bank-Marketing-Data-Analysis/master/bank-full.csv</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -670,7 +674,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>kaggle.com/c/GiveMeSomeCredit</t>
+          <t>https://raw.githubusercontent.com/JLZml/Credit-Scoring-Data-Sets/master/3.%20Kaggle/Give%20Me%20Some%20Credit/cs-training.csv</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -700,7 +704,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="55" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>MAGIC Gamma Telescope</t>
@@ -708,7 +712,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>UCI, mirror: github.com/mikeizbicki/datasets/blob/master/csv/uci/magic04.data</t>
+          <t>https://raw.githubusercontent.com/mikeizbicki/datasets/master/csv/uci/magic04.data</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -719,7 +723,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Already binary. g means gamma ray, h means hadron.</t>
+          <t>Already binary. class g means gamma ray, h means hadron.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,11 +738,11 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+          <t>CC BY 4.0. Note: file ends in .data, not .csv, but it's plain comma-separated text and opens fine in Excel or pandas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Online Shoppers Purchasing Intention</t>
@@ -746,7 +750,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>UCI, mirror: github.com/sharmaroshan/Online-Shoppers-Purchasing-Intention</t>
+          <t>https://raw.githubusercontent.com/sharmaroshan/Online-Shoppers-Purchasing-Intention/master/online_shoppers_intention.csv</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -776,7 +780,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="55" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>EEG Eye State</t>
@@ -784,7 +788,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>UCI, mirror: github.com/Krishh-mishra98/eeg-eye-state-dataset</t>
+          <t>https://raw.githubusercontent.com/Krishh-mishra98/eeg-eye-state-dataset/master/eeg.csv</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -795,7 +799,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Already binary. 1 means eyes closed, 2 means eyes open (we treat this as 0/1).</t>
+          <t>Already binary. 1 means eyes closed, 2 means eyes open (treated as 0/1).</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,7 +818,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="55" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Rain in Australia (weatherAUS)</t>
@@ -822,7 +826,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Kaggle: kaggle.com/datasets/jsphyg/weather-dataset-rattle-package, mirror: github.com/acakin/weatherAUS</t>
+          <t>https://raw.githubusercontent.com/acakin/weatherAUS/master/weatherAUS.csv</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -852,11 +856,11 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>From the Australian Bureau of Meteorology, shared on Kaggle. Check the Kaggle page for the exact reuse terms.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+          <t>From the Australian Bureau of Meteorology, shared on Kaggle. Check the Kaggle page for exact reuse terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="55" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Diabetes 130-US Hospitals</t>
@@ -864,7 +868,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>UCI, mirror: github.com/swengzju/Predicting-Diabetes-Patient-Readmission</t>
+          <t>https://raw.githubusercontent.com/swengzju/Predicting-Diabetes-Patient-Readmission/master/diabetic_data.csv</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -877,7 +881,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Was 3 classes (NO, &lt;30, &gt;30 days). We made it binary: 1 = readmitted in under 30 days, 0 = not.</t>
+          <t>Was 3 classes (NO, &lt;30, &gt;30 days). Made binary: 1 = readmitted in under 30 days, 0 = not.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -904,7 +908,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>UCI, mirror: github.com/mikeizbicki/datasets/blob/master/csv/uci/letter-recognition.data</t>
+          <t>https://raw.githubusercontent.com/mikeizbicki/datasets/master/csv/uci/letter-recognition.data</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -915,7 +919,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Was 26 classes (one per letter). We made it binary: 1 = vowel (A, E, I, O, U), 0 = consonant.</t>
+          <t>Was 26 classes (one per letter). Made binary: 1 = vowel (A, E, I, O, U), 0 = consonant.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -930,7 +934,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>CC BY 4.0. Note: file ends in .data, not .csv, but it's plain comma-separated text and opens fine in Excel or pandas.</t>
         </is>
       </c>
     </row>
@@ -942,7 +946,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>UCI, mirror: github.com/ducanng/Decision-Tree-with-scikit-learn/blob/master/connect-4.data</t>
+          <t>https://raw.githubusercontent.com/ducanng/Decision-Tree-with-scikit-learn/master/connect-4.data</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -953,7 +957,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Was 3 classes (win, loss, draw). We made it binary: 1 = win, 0 = not a win (loss or draw).</t>
+          <t>Was 3 classes (win, loss, draw). Made binary: 1 = win, 0 = not a win.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -968,7 +972,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>CC BY 4.0. Note: file ends in .data, not .csv, but it's plain comma-separated text and opens fine in Excel or pandas.</t>
         </is>
       </c>
     </row>
@@ -980,7 +984,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>UCI, mirror: github.com/mikeizbicki/datasets/blob/master/csv/uci/shuttle.tst</t>
+          <t>https://raw.githubusercontent.com/mikeizbicki/datasets/master/csv/uci/shuttle.tst</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -991,7 +995,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Was 7 classes. We made it binary: 1 = class 1 'Rad Flow', 0 = any other class.</t>
+          <t>Was 7 classes. Made binary: 1 = class 1 "Rad Flow", 0 = any other class.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1006,7 +1010,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0. Note: this is only the test portion of the full Statlog Shuttle dataset (the full set has about 58,000 rows). We could only get this file, so numbers here are for this 14,500-row file only.</t>
+          <t>CC BY 4.0. Note: this is only the test portion of the full dataset (the full set has about 58,000 rows). File ends in .tst, not .csv, but it's plain space-separated text that opens fine in Excel or pandas.</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1022,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>UCI, mirror: github.com/mikeizbicki/datasets/blob/master/csv/uci/nursery.data</t>
+          <t>https://raw.githubusercontent.com/mikeizbicki/datasets/master/csv/uci/nursery.data</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1029,7 +1033,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Was 5 classes. We made it binary: 1 = not_recom (application not recommended), 0 = any other outcome.</t>
+          <t>Was 5 classes. Made binary: 1 = not_recom (application not recommended), 0 = any other outcome.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1044,7 +1048,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>CC BY 4.0. Note: file ends in .data, not .csv, but it's plain comma-separated text and opens fine in Excel or pandas.</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1060,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>UCI, mirror: github.com/mikeizbicki/datasets/blob/master/csv/uci/krkopt.data</t>
+          <t>https://raw.githubusercontent.com/mikeizbicki/datasets/master/csv/uci/krkopt.data</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1067,7 +1071,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Was 18 classes (draw, or number of moves to win). We made it binary: 1 = draw, 0 = White wins in some number of moves.</t>
+          <t>Was 18 classes (draw, or number of moves to win). Made binary: 1 = draw, 0 = White wins in some number of moves.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1082,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>CC BY 4.0. Note: file ends in .data, not .csv, but it's plain comma-separated text and opens fine in Excel or pandas.</t>
         </is>
       </c>
     </row>
@@ -1272,34 +1276,44 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+    </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>I looked at 24 datasets in total across all rounds. 15 made it in, 9 did not.</t>
         </is>
       </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Main reason for rejecting: too few rows (6 out of 9).</t>
         </is>
       </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Other reason: could not find a working download link to check the numbers ourselves (3 out of 9: Default of Credit Card Clients, Covertype, HTRU2).</t>
         </is>
       </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A13:C13"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1310,7 +1324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1422,6 +1436,21 @@
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>For Statlog Shuttle, we could only get the 14,500-row test file, not the full ~58,000-row dataset. We used it anyway since it clears the 10,000-row minimum on its own, but we wrote clearly that it's only part of the full dataset so nobody assumes we checked the whole thing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Some of our first links pointed to a whole GitHub repo instead of the actual file, and one link (weatherAUS) looked broken when we first checked it.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>We re-checked every link and replaced each one with the exact raw file URL (the direct link to the file itself, not the repo page). All 15 now point straight at a working file. We tried uploading the actual data into this repo too, but GitHub rejected some files for being too large, so we kept this as links only, same as the assignment allows.</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1444,33 +1473,27 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Hardest rule to follow and why</t>
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>The hardest rule was checking the row count myself. It sounds simple, but two datasets I wanted to use (Default of Credit Card Clients and Covertype) could not be downloaded in this session, so I could not open the file and count the rows myself. I did not want to just use the number from the dataset page, since that is exactly what the assignment says not to do, so I left both out instead. The other tricky part was missing data. Bank Marketing has a column that is mostly filled with the word 'unknown,' and it was not obvious if that should count as missing data or not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>The hardest rule was checking the row count ourselves. It's simple once you have the file, but some datasets we wanted (Default of Credit Card Clients, Covertype, HTRU2) couldn't be downloaded in the time we had, so we couldn't open the file and count the rows ourselves. Rather than just use the number from the dataset page, which is exactly what the assignment says not to do, we left those out. We also had a link problem partway through: a couple of our early links pointed at a whole GitHub repo instead of the actual file, and one looked dead. We fixed that by re-checking every single link and replacing it with the exact raw file URL, so every source in this register points straight at a working file, not a repo homepage. The other tricky part was missing data and picking a binarisation rule -- several datasets that fit everything else had a few columns that were mostly missing (Rain in Australia, Diabetes 130-US Hospitals), so we had to decide to drop those specific columns rather than the whole dataset, and several others (Letter Recognition, Connect-4, Nursery, Chess, Shuttle) had more than two classes, so we had to pick and write down exactly which class counted as the positive one.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A3:E10"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/candidate_dataset_register.xlsx
+++ b/docs/candidate_dataset_register.xlsx
@@ -463,13 +463,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/adult-all.csv</t>
+          <t>https://archive.ics.uci.edu/static/public/2/adult.zip (click to download directly)</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/mammography.csv</t>
+          <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/mammography.csv (opens as text in browser -- use Ctrl+S / Save Page As to save it, or right-click the link and choose Save Link As)</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -598,7 +598,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/datasets/mlg-ulb/creditcardfraud</t>
+          <t>https://www.kaggle.com/datasets/mlg-ulb/creditcardfraud (click the Download button on the page -- needs a free Kaggle account)</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/khatrideepti/Bank-Marketing-Data-Analysis/master/bank-full.csv</t>
+          <t>https://archive.ics.uci.edu/static/public/222/bank+marketing.zip (click to download directly)</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/JLZml/Credit-Scoring-Data-Sets/master/3.%20Kaggle/Give%20Me%20Some%20Credit/cs-training.csv</t>
+          <t>https://www.kaggle.com/c/GiveMeSomeCredit/data (click the Download button on the page -- needs a free Kaggle account)</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -712,7 +712,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mikeizbicki/datasets/master/csv/uci/magic04.data</t>
+          <t>https://archive.ics.uci.edu/static/public/159/magic+gamma+telescope.zip (click to download directly)</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -738,7 +738,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0. Note: file ends in .data, not .csv, but it's plain comma-separated text and opens fine in Excel or pandas.</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sharmaroshan/Online-Shoppers-Purchasing-Intention/master/online_shoppers_intention.csv</t>
+          <t>https://archive.ics.uci.edu/static/public/468/online+shoppers+purchasing+intention+dataset.zip (click to download directly)</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -788,7 +788,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Krishh-mishra98/eeg-eye-state-dataset/master/eeg.csv</t>
+          <t>https://archive.ics.uci.edu/static/public/264/eeg+eye+state.zip (click to download directly)</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -826,7 +826,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/acakin/weatherAUS/master/weatherAUS.csv</t>
+          <t>https://www.kaggle.com/datasets/jsphyg/weather-dataset-rattle-package (click the Download button on the page -- needs a free Kaggle account)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/swengzju/Predicting-Diabetes-Patient-Readmission/master/diabetic_data.csv</t>
+          <t>https://archive.ics.uci.edu/static/public/296/diabetes+130-us+hospitals+for+years+1999-2008.zip (click to download directly)</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -908,7 +908,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mikeizbicki/datasets/master/csv/uci/letter-recognition.data</t>
+          <t>https://archive.ics.uci.edu/static/public/59/letter+recognition.zip (click to download directly)</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -934,7 +934,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0. Note: file ends in .data, not .csv, but it's plain comma-separated text and opens fine in Excel or pandas.</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ducanng/Decision-Tree-with-scikit-learn/master/connect-4.data</t>
+          <t>https://archive.ics.uci.edu/static/public/26/connect+4.zip (click to download directly)</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -972,7 +972,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0. Note: file ends in .data, not .csv, but it's plain comma-separated text and opens fine in Excel or pandas.</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mikeizbicki/datasets/master/csv/uci/shuttle.tst</t>
+          <t>https://archive.ics.uci.edu/static/public/148/statlog+shuttle.zip (click to download directly -- zip has both train and test files, we only checked the test file)</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0. Note: this is only the test portion of the full dataset (the full set has about 58,000 rows). File ends in .tst, not .csv, but it's plain space-separated text that opens fine in Excel or pandas.</t>
+          <t>CC BY 4.0. Note: we only checked the numbers for the 14,500-row test file inside the zip, not the full ~58,000-row training file.</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mikeizbicki/datasets/master/csv/uci/nursery.data</t>
+          <t>https://archive.ics.uci.edu/static/public/76/nursery.zip (click to download directly)</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0. Note: file ends in .data, not .csv, but it's plain comma-separated text and opens fine in Excel or pandas.</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mikeizbicki/datasets/master/csv/uci/krkopt.data</t>
+          <t>https://archive.ics.uci.edu/static/public/22/chess+king+rook+vs+king.zip (click to download directly)</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0. Note: file ends in .data, not .csv, but it's plain comma-separated text and opens fine in Excel or pandas.</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Some of our first links pointed to a whole GitHub repo instead of the actual file, and one link (weatherAUS) looked broken when we first checked it.</t>
+          <t>Our GitHub raw links pointed at the right file, but clicking them just opens a wall of text in the browser instead of downloading anything -- that's how GitHub serves raw files, not a broken link.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>We re-checked every link and replaced each one with the exact raw file URL (the direct link to the file itself, not the repo page). All 15 now point straight at a working file. We tried uploading the actual data into this repo too, but GitHub rejected some files for being too large, so we kept this as links only, same as the assignment allows.</t>
+          <t>For every dataset that lives on UCI, we switched to UCI's own official Download button link (a .zip file that actually downloads when clicked). For the two that only exist on Kaggle, we pointed to the page's Download button (needs a free Kaggle login, but that's a real download, not a text dump). Mammography doesn't have an official zip anywhere, so we kept the GitHub link but wrote in the register that you need to use Ctrl+S or Save Link As to save it, since simply clicking it just displays the text.</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>The hardest rule was checking the row count ourselves. It's simple once you have the file, but some datasets we wanted (Default of Credit Card Clients, Covertype, HTRU2) couldn't be downloaded in the time we had, so we couldn't open the file and count the rows ourselves. Rather than just use the number from the dataset page, which is exactly what the assignment says not to do, we left those out. We also had a link problem partway through: a couple of our early links pointed at a whole GitHub repo instead of the actual file, and one looked dead. We fixed that by re-checking every single link and replacing it with the exact raw file URL, so every source in this register points straight at a working file, not a repo homepage. The other tricky part was missing data and picking a binarisation rule -- several datasets that fit everything else had a few columns that were mostly missing (Rain in Australia, Diabetes 130-US Hospitals), so we had to decide to drop those specific columns rather than the whole dataset, and several others (Letter Recognition, Connect-4, Nursery, Chess, Shuttle) had more than two classes, so we had to pick and write down exactly which class counted as the positive one.</t>
+          <t>The hardest rule was checking the row count ourselves. It's simple once you have the file, but some datasets we wanted (Default of Credit Card Clients, Covertype, HTRU2) couldn't be downloaded in the time we had, so we couldn't open the file and count the rows ourselves. Rather than just use the number from the dataset page, which is exactly what the assignment says not to do, we left those out. We also had a link problem partway through: several of our links technically worked but just opened as a wall of text in the browser instead of downloading anything, since that's how GitHub serves raw files. We fixed this by switching every UCI-hosted dataset to UCI's own official Download button link, which actually saves a file, and by pointing the two Kaggle datasets at their page's Download button instead. The other tricky part was missing data and picking a binarisation rule -- several datasets that fit everything else had a few columns that were mostly missing (Rain in Australia, Diabetes 130-US Hospitals), so we had to decide to drop those specific columns rather than the whole dataset, and several others (Letter Recognition, Connect-4, Nursery, Chess, Shuttle) had more than two classes, so we had to pick and write down exactly which class counted as the positive one.</t>
         </is>
       </c>
     </row>

--- a/docs/candidate_dataset_register.xlsx
+++ b/docs/candidate_dataset_register.xlsx
@@ -469,7 +469,7 @@
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -514,7 +514,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="55" customHeight="1">
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Adult Income</t>
@@ -522,7 +522,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://archive.ics.uci.edu/static/public/2/adult.zip (click to download directly)</t>
+          <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/adult-all.csv</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -552,7 +552,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="55" customHeight="1">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Mammography</t>
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/mammography.csv (opens as text in browser -- use Ctrl+S / Save Page As to save it, or right-click the link and choose Save Link As)</t>
+          <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/mammography.csv (opens as text in browser -- use Ctrl+S / Save Page As to save it)</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -590,7 +590,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="55" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Credit Card Fraud</t>
@@ -598,7 +598,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/datasets/mlg-ulb/creditcardfraud (click the Download button on the page -- needs a free Kaggle account)</t>
+          <t>https://www.kaggle.com/datasets/mlg-ulb/creditcardfraud (click the Download button on the page -- needs a free Kaggle account, downloads as a single csv since it's a single-file dataset)</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -628,7 +628,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="55" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Bank Marketing</t>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://archive.ics.uci.edu/static/public/222/bank+marketing.zip (click to download directly)</t>
+          <t>https://raw.githubusercontent.com/khatrideepti/Bank-Marketing-Data-Analysis/master/bank-full.csv</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -666,7 +666,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="55" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Give Me Some Credit</t>
@@ -674,7 +674,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/c/GiveMeSomeCredit/data (click the Download button on the page -- needs a free Kaggle account)</t>
+          <t>https://www.kaggle.com/c/GiveMeSomeCredit/data (click the Download button on the page -- needs a free Kaggle account, downloads as a single csv since it's a single-file dataset)</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -704,7 +704,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="55" customHeight="1">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>MAGIC Gamma Telescope</t>
@@ -712,7 +712,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://archive.ics.uci.edu/static/public/159/magic+gamma+telescope.zip (click to download directly)</t>
+          <t>https://raw.githubusercontent.com/EpistasisLab/tpot/master/tutorials/MAGIC%20Gamma%20Telescope/MAGIC%20Gamma%20Telescope%20Data.csv</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -742,7 +742,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="55" customHeight="1">
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Online Shoppers Purchasing Intention</t>
@@ -750,7 +750,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://archive.ics.uci.edu/static/public/468/online+shoppers+purchasing+intention+dataset.zip (click to download directly)</t>
+          <t>https://raw.githubusercontent.com/sharmaroshan/Online-Shoppers-Purchasing-Intention/master/online_shoppers_intention.csv</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -780,7 +780,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="55" customHeight="1">
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>EEG Eye State</t>
@@ -788,7 +788,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://archive.ics.uci.edu/static/public/264/eeg+eye+state.zip (click to download directly)</t>
+          <t>https://raw.githubusercontent.com/Krishh-mishra98/eeg-eye-state-dataset/master/eeg.csv</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -818,7 +818,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="55" customHeight="1">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Rain in Australia (weatherAUS)</t>
@@ -826,7 +826,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/datasets/jsphyg/weather-dataset-rattle-package (click the Download button on the page -- needs a free Kaggle account)</t>
+          <t>https://raw.githubusercontent.com/acakin/weatherAUS/master/weatherAUS.csv</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="55" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Diabetes 130-US Hospitals</t>
@@ -868,7 +868,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://archive.ics.uci.edu/static/public/296/diabetes+130-us+hospitals+for+years+1999-2008.zip (click to download directly)</t>
+          <t>https://raw.githubusercontent.com/swengzju/Predicting-Diabetes-Patient-Readmission/master/diabetic_data.csv</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -900,7 +900,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="55" customHeight="1">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Letter Recognition</t>
@@ -908,7 +908,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://archive.ics.uci.edu/static/public/59/letter+recognition.zip (click to download directly)</t>
+          <t>https://raw.githubusercontent.com/aiez/klassif/main/letter.csv</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -934,11 +934,11 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="55" customHeight="1">
+          <t>CC BY 4.0 (original UCI data). This particular csv copy is shared under MIT by the repo maintainer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Connect-4</t>
@@ -946,7 +946,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://archive.ics.uci.edu/static/public/26/connect+4.zip (click to download directly)</t>
+          <t>https://raw.githubusercontent.com/ducanng/Decision-Tree-with-scikit-learn/master/connect-4.data (opens as text in browser -- use Ctrl+S / Save Page As to save it)</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -972,11 +972,11 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="55" customHeight="1">
+          <t>CC BY 4.0. Note: we searched for a plain .csv version of this one and couldn't find a working one, so this is a .data file -- same single comma-separated file, just an older file extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Statlog Shuttle (test split)</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://archive.ics.uci.edu/static/public/148/statlog+shuttle.zip (click to download directly -- zip has both train and test files, we only checked the test file)</t>
+          <t>https://raw.githubusercontent.com/mikeizbicki/datasets/master/csv/uci/shuttle.tst (opens as text in browser -- use Ctrl+S / Save Page As to save it)</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1010,11 +1010,11 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0. Note: we only checked the numbers for the 14,500-row test file inside the zip, not the full ~58,000-row training file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="55" customHeight="1">
+          <t>CC BY 4.0. Note: this is only the test portion of the full dataset (the full set has about 58,000 rows). We searched for a plain .csv version and couldn't find one, so this is a .tst file -- same single space-separated file, just an older file extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Nursery</t>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://archive.ics.uci.edu/static/public/76/nursery.zip (click to download directly)</t>
+          <t>https://raw.githubusercontent.com/aiez/klassif/main/nursery.csv</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1048,11 +1048,11 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="55" customHeight="1">
+          <t>CC BY 4.0 (original UCI data). This particular csv copy is shared under MIT by the repo maintainer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Chess (King-Rook vs King)</t>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://archive.ics.uci.edu/static/public/22/chess+king+rook+vs+king.zip (click to download directly)</t>
+          <t>https://raw.githubusercontent.com/mikeizbicki/datasets/master/csv/uci/krkopt.data (opens as text in browser -- use Ctrl+S / Save Page As to save it)</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>CC BY 4.0. Note: we searched for a plain .csv version of this one and couldn't find one -- there's a similarly-named 'King-Rook vs King-Pawn' dataset out there but it's a different dataset with far fewer rows, so we didn't substitute it. This is a .data file -- same single comma-separated file, just an older file extension.</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>The hardest rule was checking the row count ourselves. It's simple once you have the file, but some datasets we wanted (Default of Credit Card Clients, Covertype, HTRU2) couldn't be downloaded in the time we had, so we couldn't open the file and count the rows ourselves. Rather than just use the number from the dataset page, which is exactly what the assignment says not to do, we left those out. We also had a link problem partway through: several of our links technically worked but just opened as a wall of text in the browser instead of downloading anything, since that's how GitHub serves raw files. We fixed this by switching every UCI-hosted dataset to UCI's own official Download button link, which actually saves a file, and by pointing the two Kaggle datasets at their page's Download button instead. The other tricky part was missing data and picking a binarisation rule -- several datasets that fit everything else had a few columns that were mostly missing (Rain in Australia, Diabetes 130-US Hospitals), so we had to decide to drop those specific columns rather than the whole dataset, and several others (Letter Recognition, Connect-4, Nursery, Chess, Shuttle) had more than two classes, so we had to pick and write down exactly which class counted as the positive one.</t>
+          <t>The hardest rule was checking the row count ourselves. It's simple once you have the file, but some datasets we wanted (Default of Credit Card Clients, Covertype, HTRU2) couldn't be downloaded in the time we had, so we couldn't open the file and count the rows ourselves. Rather than just use the number from the dataset page, which is exactly what the assignment says not to do, we left those out. We also went through two rounds of link problems: first, some links pointed at a repo instead of a file, or opened as a wall of text instead of downloading; then, once we fixed that, we still wanted single .csv files with no zip to extract, so we went back and found real .csv mirrors for three more datasets (MAGIC, Letter Recognition, Nursery). Three others (Connect-4, Statlog Shuttle, Chess King-Rook vs King) still don't have a .csv version we could find, so those stay as .data/.tst files -- still a single file, just an older extension. The other tricky part was missing data and picking a binarisation rule -- several datasets that fit everything else had a few columns that were mostly missing (Rain in Australia, Diabetes 130-US Hospitals), so we had to decide to drop those specific columns rather than the whole dataset, and several others (Letter Recognition, Connect-4, Nursery, Chess, Shuttle) had more than two classes, so we had to pick and write down exactly which class counted as the positive one.</t>
         </is>
       </c>
     </row>

--- a/docs/candidate_dataset_register.xlsx
+++ b/docs/candidate_dataset_register.xlsx
@@ -514,7 +514,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Adult Income</t>
@@ -522,7 +522,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/adult-all.csv</t>
+          <t>https://www.kaggle.com/datasets/uciml/adult-census-income (Kaggle Download button, needs a free login. We verified these numbers on the same dataset via a UCI/GitHub copy, not this exact Kaggle file, since we can't download from Kaggle in our tool -- if you download this copy, do a quick row-count check yourself before trusting our numbers.)</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -552,7 +552,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
+    <row r="3" ht="70" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Mammography</t>
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/mammography.csv (opens as text in browser -- use Ctrl+S / Save Page As to save it)</t>
+          <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/mammography.csv (no Kaggle mirror of this exact tabular dataset found -- opens as text, use Ctrl+S to save)</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -590,7 +590,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="70" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Credit Card Fraud</t>
@@ -598,7 +598,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/datasets/mlg-ulb/creditcardfraud (click the Download button on the page -- needs a free Kaggle account, downloads as a single csv since it's a single-file dataset)</t>
+          <t>https://www.kaggle.com/datasets/mlg-ulb/creditcardfraud (Kaggle Download button, needs a free login, single csv)</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -628,7 +628,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="70" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Bank Marketing</t>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/khatrideepti/Bank-Marketing-Data-Analysis/master/bank-full.csv</t>
+          <t>https://www.kaggle.com/datasets/janiobachmann/bank-marketing-dataset (Kaggle Download button, needs a free login. We verified these numbers on the same dataset via a UCI/GitHub copy, not this exact Kaggle file, since we can't download from Kaggle in our tool -- if you download this copy, do a quick row-count check yourself before trusting our numbers.)</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -666,45 +666,47 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="70" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Give Me Some Credit</t>
+          <t>Default of Credit Card Clients</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/c/GiveMeSomeCredit/data (click the Download button on the page -- needs a free Kaggle account, downloads as a single csv since it's a single-file dataset)</t>
+          <t>https://raw.githubusercontent.com/YuChenAmberLu/Data-Science--Credit-Card-Default/master/UCI_Credit_Card.csv</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>150000</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>10</v>
+        <v>30000</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23 (drops the ID column)</t>
+        </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Already binary. 1 means serious default within 2 years, 0 means no default.</t>
+          <t>Already binary. default.payment.next.month: 1 = defaulted, 0 = did not.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6.7% defaulted</t>
+          <t>22.1% defaulted</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>MonthlyIncome 19.8% missing, NumberOfDependents 2.6% missing</t>
+          <t>no missing values</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Kaggle competition data, check competition rules before reuse</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>MAGIC Gamma Telescope</t>
@@ -712,7 +714,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/EpistasisLab/tpot/master/tutorials/MAGIC%20Gamma%20Telescope/MAGIC%20Gamma%20Telescope%20Data.csv</t>
+          <t>https://www.kaggle.com/datasets/abhinand05/magic-gamma-telescope-dataset (Kaggle Download button, needs a free login. We verified these numbers on the same dataset via a UCI/GitHub copy, not this exact Kaggle file, since we can't download from Kaggle in our tool -- if you download this copy, do a quick row-count check yourself before trusting our numbers.)</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -742,7 +744,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="70" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Online Shoppers Purchasing Intention</t>
@@ -750,7 +752,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sharmaroshan/Online-Shoppers-Purchasing-Intention/master/online_shoppers_intention.csv</t>
+          <t>https://www.kaggle.com/datasets/henrysue/online-shoppers-intention (Kaggle Download button, needs a free login. We verified these numbers on the same dataset via a UCI/GitHub copy, not this exact Kaggle file, since we can't download from Kaggle in our tool -- if you download this copy, do a quick row-count check yourself before trusting our numbers.)</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -780,31 +782,33 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="70" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>EEG Eye State</t>
+          <t>Skin Segmentation</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Krishh-mishra98/eeg-eye-state-dataset/master/eeg.csv</t>
+          <t>https://raw.githubusercontent.com/mikey084/Skin_segmentation/master/Skin_NonSkin.txt (tab-separated, opens as text — use Ctrl+S to save; no working .csv-named mirror found)</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>14980</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>14</v>
+        <v>245057</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3 (B, G, R colour values)</t>
+        </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Already binary. 1 means eyes closed, 2 means eyes open (treated as 0/1).</t>
+          <t>Already binary. Class 1 = skin, 2 = non-skin (treat as 0/1).</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44.9% eyes open</t>
+          <t>20.8% skin</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -818,7 +822,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="70" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Rain in Australia (weatherAUS)</t>
@@ -826,7 +830,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/acakin/weatherAUS/master/weatherAUS.csv</t>
+          <t>https://www.kaggle.com/datasets/jsphyg/weather-dataset-rattle-package (Kaggle Download button, needs a free login)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -860,7 +864,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="70" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Diabetes 130-US Hospitals</t>
@@ -868,7 +872,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/swengzju/Predicting-Diabetes-Patient-Readmission/master/diabetic_data.csv</t>
+          <t>https://www.kaggle.com/datasets/anushrevankar/uci-diabetes-130-us-hospitals-dataset (Kaggle Download button, needs a free login. We verified these numbers on the same dataset via a UCI/GitHub copy, not this exact Kaggle file, since we can't download from Kaggle in our tool -- if you download this copy, do a quick row-count check yourself before trusting our numbers.)</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -900,7 +904,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Letter Recognition</t>
@@ -908,7 +912,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aiez/klassif/main/letter.csv</t>
+          <t>https://www.kaggle.com/datasets/datajameson/letter-recognition-dataset (Kaggle Download button, needs a free login. We verified these numbers on the same dataset via a UCI/GitHub copy, not this exact Kaggle file, since we can't download from Kaggle in our tool -- if you download this copy, do a quick row-count check yourself before trusting our numbers.)</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -934,11 +938,11 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0 (original UCI data). This particular csv copy is shared under MIT by the repo maintainer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Connect-4</t>
@@ -946,7 +950,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ducanng/Decision-Tree-with-scikit-learn/master/connect-4.data (opens as text in browser -- use Ctrl+S / Save Page As to save it)</t>
+          <t>https://www.kaggle.com/datasets/tbrewer/connect-4 (Kaggle Download button, needs a free login. We verified these numbers on the same dataset via a UCI/GitHub copy, not this exact Kaggle file, since we can't download from Kaggle in our tool -- if you download this copy, do a quick row-count check yourself before trusting our numbers.)</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -972,35 +976,35 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0. Note: we searched for a plain .csv version of this one and couldn't find a working one, so this is a .data file -- same single comma-separated file, just an older file extension.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+          <t>Shared by the uploader as 'use as you see fit' -- original data is CC BY 4.0 via UCI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Statlog Shuttle (test split)</t>
+          <t>Internet Firewall Data</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mikeizbicki/datasets/master/csv/uci/shuttle.tst (opens as text in browser -- use Ctrl+S / Save Page As to save it)</t>
+          <t>https://raw.githubusercontent.com/semnan-university-ai/Internet-Firewall/master/firewall.csv</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>14500</v>
+        <v>65532</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Was 7 classes. Made binary: 1 = class 1 "Rad Flow", 0 = any other class.</t>
+          <t>Was 4 classes (allow, deny, drop, reset-both). Made binary: 1 = allow, 0 = not allowed.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20.8% not class 1</t>
+          <t>42.6% not allowed</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1010,11 +1014,11 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0. Note: this is only the test portion of the full dataset (the full set has about 58,000 rows). We searched for a plain .csv version and couldn't find one, so this is a .tst file -- same single space-separated file, just an older file extension.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="70" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Nursery</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aiez/klassif/main/nursery.csv</t>
+          <t>https://www.kaggle.com/datasets/iamashwinks/nursery-dataset (Kaggle Download button, needs a free login. We verified these numbers on the same dataset via a UCI/GitHub copy, not this exact Kaggle file, since we can't download from Kaggle in our tool -- if you download this copy, do a quick row-count check yourself before trusting our numbers.)</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1048,35 +1052,35 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0 (original UCI data). This particular csv copy is shared under MIT by the repo maintainer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Chess (King-Rook vs King)</t>
+          <t>Avila (training split)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/mikeizbicki/datasets/master/csv/uci/krkopt.data (opens as text in browser -- use Ctrl+S / Save Page As to save it)</t>
+          <t>https://raw.githubusercontent.com/simonharris/cleandata/master/offline_data/AvilaTR.csv</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>28056</v>
+        <v>10430</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Was 18 classes (draw, or number of moves to win). Made binary: 1 = draw, 0 = White wins in some number of moves.</t>
+          <t>Was 12 classes (scribe styles A–Y). Made binary: 1 = class A, 0 = any other class.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10.0% draw</t>
+          <t>41.1% class A</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1090,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0. Note: we searched for a plain .csv version of this one and couldn't find one -- there's a similarly-named 'King-Rook vs King-Pawn' dataset out there but it's a different dataset with far fewer rows, so we didn't substitute it. This is a .data file -- same single comma-separated file, just an older file extension.</t>
+          <t>CC BY 4.0. Note: this is the training split only; the full Avila dataset (train+test) is about 20,867 rows.</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1419,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>For datasets with more than 2 classes (Letter Recognition, Connect-4, Nursery, Chess, Shuttle), which class do we pick to turn it binary?</t>
+          <t>For datasets with more than 2 classes (Letter Recognition, Connect-4, Nursery, Avila, Internet Firewall), which class do we pick to turn it binary?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1489,7 +1493,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>The hardest rule was checking the row count ourselves. It's simple once you have the file, but some datasets we wanted (Default of Credit Card Clients, Covertype, HTRU2) couldn't be downloaded in the time we had, so we couldn't open the file and count the rows ourselves. Rather than just use the number from the dataset page, which is exactly what the assignment says not to do, we left those out. We also went through two rounds of link problems: first, some links pointed at a repo instead of a file, or opened as a wall of text instead of downloading; then, once we fixed that, we still wanted single .csv files with no zip to extract, so we went back and found real .csv mirrors for three more datasets (MAGIC, Letter Recognition, Nursery). Three others (Connect-4, Statlog Shuttle, Chess King-Rook vs King) still don't have a .csv version we could find, so those stay as .data/.tst files -- still a single file, just an older extension. The other tricky part was missing data and picking a binarisation rule -- several datasets that fit everything else had a few columns that were mostly missing (Rain in Australia, Diabetes 130-US Hospitals), so we had to decide to drop those specific columns rather than the whole dataset, and several others (Letter Recognition, Connect-4, Nursery, Chess, Shuttle) had more than two classes, so we had to pick and write down exactly which class counted as the positive one.</t>
+          <t>The hardest rule was checking the row count ourselves. It's simple once you have the file, but some datasets we wanted (Default of Credit Card Clients, Covertype, HTRU2) couldn't be downloaded in the time we had, so we couldn't open the file and count the rows ourselves. Rather than just use the number from the dataset page, which is exactly what the assignment says not to do, we left those out. Later we were asked to move everything onto Kaggle for a cleaner download experience, and we found real Kaggle pages for 13 of our 15 datasets -- but we can't actually download from Kaggle in our own tool, since it needs a login. So for those 13, the numbers in this register come from checking the same dataset on UCI or GitHub, not from downloading the exact Kaggle file, and we said so directly rather than pretend we'd re-verified something we hadn't. Two datasets (Mammography, Chess King-Rook vs King) had no Kaggle version we could find at all, so those stayed on their original source. The other tricky part was missing data and picking a binarisation rule -- several datasets that fit everything else had a few columns that were mostly missing (Rain in Australia, Diabetes 130-US Hospitals), so we had to decide to drop those specific columns rather than the whole dataset, and several others (Letter Recognition, Connect-4, Nursery, Avila, Internet Firewall) had more than two classes, so we had to pick and write down exactly which class counted as the positive one.</t>
         </is>
       </c>
     </row>

--- a/docs/candidate_dataset_register.xlsx
+++ b/docs/candidate_dataset_register.xlsx
@@ -39,8 +39,9 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="13"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -82,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -90,7 +91,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -462,14 +467,14 @@
   <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="65" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -514,15 +519,16 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="70" customHeight="1">
+    <row r="2" ht="75" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Adult Income</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kaggle.com/datasets/uciml/adult-census-income (Kaggle Download button, needs a free login. We verified these numbers on the same dataset via a UCI/GitHub copy, not this exact Kaggle file, since we can't download from Kaggle in our tool -- if you download this copy, do a quick row-count check yourself before trusting our numbers.)</t>
+          <t>Adult (Census Income)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/adult-all.csv
+(origin: UCI)</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -533,34 +539,35 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Already binary. Income is either &lt;=50K or &gt;50K.</t>
+          <t>Already binary. income: &gt;50K = 1, &lt;=50K = 0.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>23.9% earn &gt;50K</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>workclass 5.7% missing, occupation 5.8% missing, native_country 1.8% missing</t>
+          <t>3 columns: workclass 5.7%, occupation 5.8%, native-country 1.8% (coded '?')</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
+          <t>CC BY 4.0 (UCI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="75" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Mammography</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/mammography.csv (no Kaggle mirror of this exact tabular dataset found -- opens as text, use Ctrl+S to save)</t>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/jbrownlee/Datasets/master/mammography.csv
+(origin: OpenML/KEEL)</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -571,34 +578,35 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Already binary. class 1 means calcification found, -1 means not found.</t>
+          <t>Already binary. class: '1' (calcification) = 1, '-1' = 0.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2.3% positive</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>no missing values</t>
+          <t>0%, 0 columns</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Public benchmark dataset, free to use</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
+          <t>No explicit licence found; widely mirrored benchmark. Check before redistributing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="75" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Credit Card Fraud</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kaggle.com/datasets/mlg-ulb/creditcardfraud (Kaggle Download button, needs a free login, single csv)</t>
+          <t>Credit Card Fraud (ULB)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/mlg-ulb/creditcardfraud
+(Kaggle page; we counted the rows on a mirror of the same file, not on the Kaggle download)</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -609,34 +617,35 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Already binary. 1 means fraud, 0 means normal transaction.</t>
+          <t>Already binary. Class: 1 = fraud, 0 = genuine.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0.17% fraud</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>no missing values</t>
+          <t>0%, 0 columns</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Open Database License (DbCL) v1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
+          <t>DbCL v1.0 (Kaggle page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="75" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Bank Marketing</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kaggle.com/datasets/janiobachmann/bank-marketing-dataset (Kaggle Download button, needs a free login. We verified these numbers on the same dataset via a UCI/GitHub copy, not this exact Kaggle file, since we can't download from Kaggle in our tool -- if you download this copy, do a quick row-count check yourself before trusting our numbers.)</t>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/khatrideepti/Bank-Marketing-Data-Analysis/master/bank-full.csv
+(origin: UCI, semicolon-separated)</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -647,74 +656,74 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Already binary. Customer said yes or no to the offer.</t>
+          <t>Already binary. y: yes = 1, no = 0.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11.7% said yes</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>no blank cells, but the poutcome column is 81.7% marked unknown</t>
+          <t>0% null. 'unknown' is used as a category: poutcome 81.7%, contact 28.8%, education 4.1%, job 0.6%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
+          <t>CC BY 4.0 (UCI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="75" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Default of Credit Card Clients</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/YuChenAmberLu/Data-Science--Credit-Card-Default/master/UCI_Credit_Card.csv</t>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/YuChenAmberLu/Data-Science--Credit-Card-Default/master/UCI_Credit_Card.csv
+(origin: UCI)</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>23 (drops the ID column)</t>
-        </is>
+      <c r="D6" s="2" t="n">
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Already binary. default.payment.next.month: 1 = defaulted, 0 = did not.</t>
+          <t>Already binary. default.payment.next.month: 1 = default, 0 = no default. ID column excluded from the feature count.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22.1% defaulted</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>no missing values</t>
+          <t>0%, 0 columns</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
+          <t>CC BY 4.0 (UCI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="75" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>MAGIC Gamma Telescope</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kaggle.com/datasets/abhinand05/magic-gamma-telescope-dataset (Kaggle Download button, needs a free login. We verified these numbers on the same dataset via a UCI/GitHub copy, not this exact Kaggle file, since we can't download from Kaggle in our tool -- if you download this copy, do a quick row-count check yourself before trusting our numbers.)</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/EpistasisLab/tpot/master/tutorials/MAGIC%20Gamma%20Telescope/MAGIC%20Gamma%20Telescope%20Data.csv
+(origin: UCI)</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -725,34 +734,35 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Already binary. class g means gamma ray, h means hadron.</t>
+          <t>Already binary. Class: h (hadron) = 1, g (gamma) = 0.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35.2% are hadron</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>no missing values</t>
+          <t>0%, 0 columns</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
+          <t>CC BY 4.0 (UCI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="75" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Online Shoppers Purchasing Intention</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kaggle.com/datasets/henrysue/online-shoppers-intention (Kaggle Download button, needs a free login. We verified these numbers on the same dataset via a UCI/GitHub copy, not this exact Kaggle file, since we can't download from Kaggle in our tool -- if you download this copy, do a quick row-count check yourself before trusting our numbers.)</t>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sharmaroshan/Online-Shoppers-Purchasing-Intention/master/online_shoppers_intention.csv
+(origin: UCI)</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -763,308 +773,308 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Already binary. Revenue is True if the visit ended in a purchase, False if not.</t>
+          <t>Already binary. Revenue: True = 1, False = 0.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15.5% ended in a purchase</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>no missing values</t>
+          <t>0%, 0 columns</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="70" customHeight="1">
+          <t>CC BY 4.0 (UCI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="75" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Rain in Australia (weatherAUS)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/acakin/weatherAUS/master/weatherAUS.csv
+(origin: Kaggle, Bureau of Meteorology data)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>142193</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Already binary. RainTomorrow: Yes = 1, No = 0. 3,267 of 145,460 rows dropped for a missing target. Date and Location excluded.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4 columns over 30% (Sunshine 47.7%, Evaporation 42.8%, Cloud3pm 40.2%, Cloud9am 37.7%), to be dropped. Worst kept column: Pressure9am 9.9%. (Percentages are out of the 142,193 rows with a target.)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Bureau of Meteorology data via Kaggle; reuse terms on the Kaggle page</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="75" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Diabetes 130-US Hospitals</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/swengzju/Predicting-Diabetes-Patient-Readmission/master/diabetic_data.csv
+(origin: UCI)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>101766</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3 classes (NO, &gt;30, &lt;30). Binarised: readmitted '&lt;30' = 1, all others = 0.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11.2%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5 columns over 30% (weight 96.9%, max_glu_serum 94.7%, A1Cresult 83.3%, medical_specialty 49.1%, payer_code 39.6%), to be dropped. Worst kept column: race 2.2%.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>CC BY 4.0 (UCI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="75" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Letter Recognition</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aiez/klassif/main/letter.csv
+(origin: UCI)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26 classes (letters). Binarised: vowel (A, E, I, O, U) = 1, consonant = 0.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19.4%</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0%, 0 columns</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>CC BY 4.0 (UCI original); this copy is a third-party mirror</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="75" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Connect-4</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ducanng/Decision-Tree-with-scikit-learn/master/connect-4.data
+(origin: UCI; .data extension, comma-separated)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>67557</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3 classes (win, loss, draw). Binarised: not-win (loss or draw) = 1, win = 0, so that the minority class is 1.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>34.2%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0%, 0 columns</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>CC BY 4.0 (UCI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="75" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Nursery</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/aiez/klassif/main/nursery.csv
+(origin: UCI)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>12960</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5 classes. Binarised: not_recom = 1, all others = 0.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0%, 0 columns</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>CC BY 4.0 (UCI original); this copy is a third-party mirror</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="75" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>Skin Segmentation</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/mikey084/Skin_segmentation/master/Skin_NonSkin.txt (tab-separated, opens as text — use Ctrl+S to save; no working .csv-named mirror found)</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/mikey084/Skin_segmentation/master/Skin_NonSkin.txt
+(origin: UCI; .txt extension, tab-separated, no header)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
         <v>245057</v>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3 (B, G, R colour values)</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Already binary. Class 1 = skin, 2 = non-skin (treat as 0/1).</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>20.8% skin</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>no missing values</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>CC BY 4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Rain in Australia (weatherAUS)</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kaggle.com/datasets/jsphyg/weather-dataset-rattle-package (Kaggle Download button, needs a free login)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>142193 usable (145460 total, 3267 rows dropped for missing target)</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>16 (dropped Date, Location, and 4 columns over 30% missing: Sunshine, Evaporation, Cloud9am, Cloud3pm)</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Already binary. RainTomorrow is Yes or No.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22.4% said Yes</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>worst kept column (Pressure9am) is 9.9% missing, after dropping the 4 columns above</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>From the Australian Bureau of Meteorology, shared on Kaggle. Check the Kaggle page for exact reuse terms.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Diabetes 130-US Hospitals</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kaggle.com/datasets/anushrevankar/uci-diabetes-130-us-hospitals-dataset (Kaggle Download button, needs a free login. We verified these numbers on the same dataset via a UCI/GitHub copy, not this exact Kaggle file, since we can't download from Kaggle in our tool -- if you download this copy, do a quick row-count check yourself before trusting our numbers.)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>101766</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>42 (dropped 2 ID columns, and 5 columns over 30% missing: weight, max_glu_serum, A1Cresult, medical_specialty, payer_code)</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Was 3 classes (NO, &lt;30, &gt;30 days). Made binary: 1 = readmitted in under 30 days, 0 = not.</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11.2% readmitted under 30 days</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>worst kept column (race) is 2.2% missing, after dropping the 5 columns above</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>CC BY 4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Letter Recognition</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kaggle.com/datasets/datajameson/letter-recognition-dataset (Kaggle Download button, needs a free login. We verified these numbers on the same dataset via a UCI/GitHub copy, not this exact Kaggle file, since we can't download from Kaggle in our tool -- if you download this copy, do a quick row-count check yourself before trusting our numbers.)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Was 26 classes (one per letter). Made binary: 1 = vowel (A, E, I, O, U), 0 = consonant.</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19.4% vowels</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>no missing values</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>CC BY 4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Connect-4</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kaggle.com/datasets/tbrewer/connect-4 (Kaggle Download button, needs a free login. We verified these numbers on the same dataset via a UCI/GitHub copy, not this exact Kaggle file, since we can't download from Kaggle in our tool -- if you download this copy, do a quick row-count check yourself before trusting our numbers.)</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>67557</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Was 3 classes (win, loss, draw). Made binary: 1 = win, 0 = not a win.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34.2% not a win</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>no missing values</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Shared by the uploader as 'use as you see fit' -- original data is CC BY 4.0 via UCI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Already binary. Fourth column: 1 = skin, 2 = non-skin. Skin recoded to 1, non-skin to 0.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0%, 0 columns</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>CC BY 4.0 (UCI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="75" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Internet Firewall Data</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/semnan-university-ai/Internet-Firewall/master/firewall.csv</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/semnan-university-ai/Internet-Firewall/master/firewall.csv
+(origin: UCI)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
         <v>65532</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D15" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Was 4 classes (allow, deny, drop, reset-both). Made binary: 1 = allow, 0 = not allowed.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>42.6% not allowed</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>no missing values</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>CC BY 4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="70" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Nursery</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kaggle.com/datasets/iamashwinks/nursery-dataset (Kaggle Download button, needs a free login. We verified these numbers on the same dataset via a UCI/GitHub copy, not this exact Kaggle file, since we can't download from Kaggle in our tool -- if you download this copy, do a quick row-count check yourself before trusting our numbers.)</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>12960</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Was 5 classes. Made binary: 1 = not_recom (application not recommended), 0 = any other outcome.</t>
+          <t>4 classes in Action (allow, deny, drop, reset-both). Binarised: not-allow (deny, drop, reset-both) = 1, allow = 0.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33.3% not_recom</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>no missing values</t>
+          <t>0%, 0 columns</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="70" customHeight="1">
+          <t>CC BY 4.0 (UCI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="75" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Avila (training split)</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/simonharris/cleandata/master/offline_data/AvilaTR.csv</t>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/simonharris/cleandata/master/offline_data/AvilaTR.csv
+(origin: UCI; no header)</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1075,26 +1085,43 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Was 12 classes (scribe styles A–Y). Made binary: 1 = class A, 0 = any other class.</t>
+          <t>12 classes (scribe styles). Binarised: class A = 1, all others = 0. Training split only (full dataset is about 20,867 rows).</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41.1% class A</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>no missing values</t>
+          <t>0%, 0 columns</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>CC BY 4.0. Note: this is the training split only; the full Avila dataset (train+test) is about 20,867 rows.</t>
+          <t>CC BY 4.0 (UCI)</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1105,12 +1132,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,198 +1153,266 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Why I rejected it</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
+          <t>Why rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Phoneme</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>5404</v>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>5,404</t>
+        </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Too few rows, needs at least 10,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
+          <t>Under 10,000 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Oil Spill</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>937</v>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Too few rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>Under 10,000 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Sonar</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>208</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Too few rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>Under 10,000 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Pima Indians Diabetes</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>768</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Too few rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>Under 10,000 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>German Credit</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>1000</v>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Too few rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>Under 10,000 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Telco Customer Churn</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>7043</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>7,043</t>
+        </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Too few rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t>Under 10,000 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>IBM HR Attrition</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>1470</v>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1,470</t>
+        </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Too few rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+          <t>Under 10,000 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Default of Credit Card Clients</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>30000</v>
+          <t>Covertype</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>not verified</t>
+        </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Row count looks fine but I could not download the actual file to check it myself, so I left it out</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
+          <t>No downloadable file we could load and count. It would also need a binarisation rule (7 classes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Covertype</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>581012</v>
+          <t>HTRU2 (Pulsar)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>not verified</t>
+        </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Row count looks fine but I could not download the file, and it also needs a binarisation rule since it has 7 classes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
+          <t>No working download link found, so the row count could not be checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HTRU2 (Pulsar Detection)</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>17898</v>
+          <t>Give Me Some Credit</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>not verified</t>
+        </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Row count looks fine (17,898) but we could not find a working raw file link to download and check it ourselves, so we left it out</t>
+          <t>The Kaggle download did not work for the group, so the file could not be loaded and counted.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>EEG Eye State</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>14,980 in the UCI copy we checked; about 4,900 in the copy the group downloaded</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>The two copies disagree, and we could not settle which is right. Dropped rather than guess.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Statlog Shuttle</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>14,500 (test file only)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Only a .tst test-split file was reachable, not a single csv with all rows.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>I looked at 24 datasets in total across all rounds. 15 made it in, 9 did not.</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Main reason for rejecting: too few rows (6 out of 9).</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
+          <t>Chess (King-Rook vs King)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>28,056</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Only available as a .data file with no csv version found.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Other reason: could not find a working download link to check the numbers ourselves (3 out of 9: Default of Credit Card Clients, Covertype, HTRU2).</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>We examined 28 datasets in total. 15 are in the register and 13 were rejected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Most common reason: under 10,000 rows (7 of 13).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Second most common: no downloadable csv we could load and count (5 of 13: Covertype, HTRU2, Give Me Some Credit, Statlog Shuttle, Chess).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Third: two copies of the same dataset disagreed on row count (1 of 13: EEG Eye State).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A16:C16"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1333,7 +1428,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1344,117 +1439,117 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Thing that was not clear</t>
+          <t>What was unclear</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>What I did about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45" customHeight="1">
+          <t>What we decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>In Bank Marketing, one column is 81.7% marked 'unknown'. Is that missing data or just a normal answer?</t>
+          <t>Is 'unknown' in Bank Marketing missing data?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>I counted it as a normal answer, not missing data, since it means 'no past contact.' Someone else might count it as missing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="45" customHeight="1">
+          <t>Counted as a category, not as missing. poutcome is 81.7% 'unknown', which would fail the 30% rule if counted as missing. A stricter reading would drop that column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>What counts as a 'feature' vs an ID column?</t>
+          <t>What counts as an identifier column?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>I dropped any column that was just a row number or ID, since it has no predictive use.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
+          <t>Dropped pure row numbers and IDs (e.g. ID in Default of Credit Card Clients). The brief gives no rule for near-unique columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>What to do when the published row count looks fine but I can't download the file myself?</t>
+          <t>Does the 30% rule apply per column or per dataset?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>I left those datasets out instead of trusting the number, since the assignment says to check it myself.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
+          <t>Read as per column, as written. Columns over 30% are dropped, not the whole dataset (Rain in Australia, Diabetes 130).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Is Kaggle competition data the same as regular Kaggle dataset licensing?</t>
+          <t>How to binarise a many-class target?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>I kept Give Me Some Credit in the list but flagged that competition rules are stricter and should be double checked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="55" customHeight="1">
+          <t>Chose a split that makes sense for each dataset (vowel/consonant, win/not-win, class A/other). A different choice would change prevalence and difficulty, so it is a research decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>For datasets with more than 2 classes (Letter Recognition, Connect-4, Nursery, Avila, Internet Firewall), which class do we pick to turn it binary?</t>
+          <t>Can a dataset be used if only part of it is available?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>We picked the split that made the most real-world sense for each one (e.g. vowel vs consonant, win vs not-win, draw vs not-draw) rather than just picking the biggest class. A different choice would give a different minority percent, so this is a real decision, not just a formatting step.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="55" customHeight="1">
+          <t>Avila is the training split only (10,430 rows, close to the 10,000 limit). Statlog Shuttle was dropped for this reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Is it OK to use just part of a dataset if that's the only file we could access?</t>
+          <t>Which copy of a dataset is the real one?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>For Statlog Shuttle, we could only get the 14,500-row test file, not the full ~58,000-row dataset. We used it anyway since it clears the 10,000-row minimum on its own, but we wrote clearly that it's only part of the full dataset so nobody assumes we checked the whole thing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
+          <t>Row counts were checked on one copy of each file. EEG Eye State showed that two copies can disagree, so the count has to be re-checked on the exact file used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Our GitHub raw links pointed at the right file, but clicking them just opens a wall of text in the browser instead of downloading anything -- that's how GitHub serves raw files, not a broken link.</t>
+          <t>Do .data and .txt files count as csv?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>For every dataset that lives on UCI, we switched to UCI's own official Download button link (a .zip file that actually downloads when clicked). For the two that only exist on Kaggle, we pointed to the page's Download button (needs a free Kaggle login, but that's a real download, not a text dump). Mammography doesn't have an official zip anywhere, so we kept the GitHub link but wrote in the register that you need to use Ctrl+S or Save Link As to save it, since simply clicking it just displays the text.</t>
+          <t>Connect-4 (.data) and Skin Segmentation (.txt) are plain delimited text, but not named .csv. Kept and flagged.</t>
         </is>
       </c>
     </row>
@@ -1469,35 +1564,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Hardest rule to follow and why</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Hardest criterion to apply, and why</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>The hardest rule was checking the row count ourselves. It's simple once you have the file, but some datasets we wanted (Default of Credit Card Clients, Covertype, HTRU2) couldn't be downloaded in the time we had, so we couldn't open the file and count the rows ourselves. Rather than just use the number from the dataset page, which is exactly what the assignment says not to do, we left those out. Later we were asked to move everything onto Kaggle for a cleaner download experience, and we found real Kaggle pages for 13 of our 15 datasets -- but we can't actually download from Kaggle in our own tool, since it needs a login. So for those 13, the numbers in this register come from checking the same dataset on UCI or GitHub, not from downloading the exact Kaggle file, and we said so directly rather than pretend we'd re-verified something we hadn't. Two datasets (Mammography, Chess King-Rook vs King) had no Kaggle version we could find at all, so those stayed on their original source. The other tricky part was missing data and picking a binarisation rule -- several datasets that fit everything else had a few columns that were mostly missing (Rain in Australia, Diabetes 130-US Hospitals), so we had to decide to drop those specific columns rather than the whole dataset, and several others (Letter Recognition, Connect-4, Nursery, Avila, Internet Firewall) had more than two classes, so we had to pick and write down exactly which class counted as the positive one.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>The hardest rule was checking the row count ourselves. Loading a file and counting is easy once you have the file. The problem was getting a file we could trust. Several datasets (Covertype, HTRU2, Give Me Some Credit) could not be downloaded in a form we could load, so we could not count them and left them out instead of copying a number from a dataset page. EEG Eye State was the clearest example of why the rule exists: one copy had 14,980 rows and another had about 4,900, so a published count alone would have been wrong for one of them. The next hardest was missing data, because 'unknown' in Bank Marketing is not a null but would break the 30% rule if counted as one. Binarising many-class targets (Letter Recognition, Connect-4, Nursery, Avila, Firewall) was also a real choice, since each split gives a different prevalence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:F16"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>